--- a/input/reg_health_wellbeing.xlsx
+++ b/input/reg_health_wellbeing.xlsx
@@ -1,36 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\andy_local\SimPaths project files\InitialPopulationCreation\regression_estimates\results\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C830BB4-050A-4122-88F4-08CF8C565FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="10"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="Gof" sheetId="2" r:id="rId2"/>
-    <sheet name="DHE_MCS1" sheetId="3" r:id="rId3"/>
-    <sheet name="DHE_MCS2_Females" sheetId="4" r:id="rId4"/>
-    <sheet name="DHE_MCS2_Males" sheetId="5" r:id="rId5"/>
-    <sheet name="DHE_PCS1" sheetId="6" r:id="rId6"/>
-    <sheet name="DHE_PCS2_Females" sheetId="7" r:id="rId7"/>
-    <sheet name="DHE_PCS2_Males" sheetId="8" r:id="rId8"/>
-    <sheet name="DLS1" sheetId="9" r:id="rId9"/>
-    <sheet name="DLS2_Females" sheetId="10" r:id="rId10"/>
-    <sheet name="DLS2_Males" sheetId="11" r:id="rId11"/>
+    <sheet name="Info" sheetId="1" r:id="rId2"/>
+    <sheet name="Gof" sheetId="2" r:id="rId4"/>
+    <sheet name="DHE_MCS1" sheetId="3" r:id="rId5"/>
+    <sheet name="DHE_MCS2_Females" sheetId="4" r:id="rId6"/>
+    <sheet name="DHE_MCS2_Males" sheetId="5" r:id="rId7"/>
+    <sheet name="DHE_PCS1" sheetId="6" r:id="rId8"/>
+    <sheet name="DHE_PCS2_Females" sheetId="7" r:id="rId9"/>
+    <sheet name="DHE_PCS2_Males" sheetId="8" r:id="rId10"/>
+    <sheet name="DLS1" sheetId="9" r:id="rId11"/>
+    <sheet name="DLS2_Females" sheetId="10" r:id="rId12"/>
+    <sheet name="DLS2_Males" sheetId="11" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="0" fullCalcOnLoad="true"/>
+  <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="892" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="401" uniqueCount="83">
   <si>
     <t>Description:</t>
   </si>
@@ -218,6 +211,9 @@
     <t>N</t>
   </si>
   <si>
+    <t>VARIANCE</t>
+  </si>
+  <si>
     <t>PersistentEmployed</t>
   </si>
   <si>
@@ -251,18 +247,6 @@
     <t>D_Econ_benefits_UC</t>
   </si>
   <si>
-    <t>D_Econ_benefits_UC_Lhw_TEN</t>
-  </si>
-  <si>
-    <t>D_Econ_benefits_UC_Lhw_TWENTY</t>
-  </si>
-  <si>
-    <t>D_Econ_benefits_UC_Lhw_THIRTY</t>
-  </si>
-  <si>
-    <t>D_Econ_benefits_UC_Lhw_FORTY</t>
-  </si>
-  <si>
     <t>DHE_MCS2_Females: SF12 MCS Score (0-100)</t>
   </si>
   <si>
@@ -289,219 +273,132 @@
   <si>
     <t>DLS2_Males: Life Satisfaction Score (0-10)</t>
   </si>
-  <si>
-    <t>EmployedToUnemployed</t>
-  </si>
-  <si>
-    <t>NonPovertyToPoverty</t>
-  </si>
-  <si>
-    <t>VARIANCE</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="40">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -512,98 +409,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="27">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -706,70 +512,57 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -777,348 +570,23 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="true">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="true">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="true">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1126,20 +594,20 @@
         <v>3</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1147,7 +615,7 @@
         <v>7</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1155,7 +623,7 @@
         <v>9</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1163,7 +631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1171,7 +639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1179,7 +647,7 @@
         <v>15</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1187,7 +655,7 @@
         <v>17</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1195,7 +663,7 @@
         <v>19</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1203,7 +671,7 @@
         <v>21</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1212,16 +680,15 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1229,587 +696,455 @@
         <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>63</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2">
+        <v>0.10789640662516291</v>
+      </c>
+      <c r="C2">
+        <v>0.0018448433040586713</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>64</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B3">
+        <v>0.21556334863257032</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0.0035548242092530869</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>65</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B4">
+        <v>0.04460068370727751</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0.0022420596186237566</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>66</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B5">
+        <v>0.020051459966007424</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0.0014352583156351684</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>67</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B6">
+        <v>-0.011693139587696326</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0.0021888501182822924</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
         <v>68</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B7">
+        <v>-0.02767743861299142</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0.0024333857509374634</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
         <v>69</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B8">
+        <v>-0.014282128349269166</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.00027183380311141642</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
         <v>70</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B9">
+        <v>0.024815487466412926</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.00029832937935414137</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
         <v>71</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B10">
+        <v>-0.97453682972644906</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.001416888399495033</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
         <v>72</v>
       </c>
-      <c r="N1" t="s">
+      <c r="B11">
+        <v>-0.015915818491091791</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.00060992593667875191</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
         <v>73</v>
       </c>
-      <c r="O1" t="s">
-        <v>74</v>
-      </c>
-      <c r="P1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2">
-        <v>-0.023377323424163019</v>
-      </c>
-      <c r="C2">
-        <v>0.0062140995108060666</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3">
-        <v>0.08021207610363372</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0.0075458582994253828</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4">
-        <v>0.062118951453237724</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0.0022566904044785592</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5">
-        <v>0.020873041228790981</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0.0014299428081443796</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6">
-        <v>-0.011427183180818454</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0.0021857806257038091</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7">
-        <v>-0.025799363815819543</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0.0024337805359797584</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8">
-        <v>-0.015401854543178333</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0.00027201407732038274</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9">
-        <v>0.026423316605889202</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0.00030299826207296767</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10">
-        <v>-0.97638855963467364</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0.0014127477678230651</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11">
-        <v>-0.022695628963565299</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0.00061386056209909539</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>72</v>
-      </c>
       <c r="B12">
-        <v>-0.13848483707746415</v>
+        <v>-0.093329799383714093</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1842,244 +1177,19 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.0077353917202114698</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13">
-        <v>-0.24085566944970102</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0.042493000110619024</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14">
-        <v>0.066035007920236602</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0.01944372724259024</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15">
-        <v>0.029647083286058262</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0.027564890735656055</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16">
-        <v>0.24596481370669318</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0.025322509912826786</v>
+        <v>0.0039242289902112074</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -2087,587 +1197,455 @@
         <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>63</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2">
+        <v>0.15207044694444188</v>
+      </c>
+      <c r="C2">
+        <v>0.0029554171792980765</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>64</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B3">
+        <v>0.14854706699197426</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0.0068614596513076193</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>65</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B4">
+        <v>-0.054133050290819683</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0.0041576882487216124</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>66</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B5">
+        <v>0.055091047842367888</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0.0020656459495944704</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>67</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B6">
+        <v>0.029699867875583923</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0.0029846315435302427</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
         <v>68</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B7">
+        <v>0.10757347246749741</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0.003691277414159394</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
         <v>69</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B8">
+        <v>-0.055394305240049395</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.00029355205374676429</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
         <v>70</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B9">
+        <v>-0.012480849790909564</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.00032068523104581922</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
         <v>71</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B10">
+        <v>-1.0199254476997115</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.0020646474329921879</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
         <v>72</v>
       </c>
-      <c r="N1" t="s">
+      <c r="B11">
+        <v>-0.049231938773035396</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.00073749723803681448</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
         <v>73</v>
       </c>
-      <c r="O1" t="s">
-        <v>74</v>
-      </c>
-      <c r="P1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2">
-        <v>-0.23327887966804461</v>
-      </c>
-      <c r="C2">
-        <v>0.016424277059865582</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3">
-        <v>-0.23355339632286223</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0.019422904676379537</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4">
-        <v>-0.034782314840978511</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0.0041888923761831789</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5">
-        <v>0.049589458620550191</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0.0020729460310861549</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6">
-        <v>0.025817702707921081</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0.0029820578788989287</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7">
-        <v>0.10684200049530425</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0.0036897608535200279</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8">
-        <v>-0.055226579698723612</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0.00029276880434437106</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9">
-        <v>-0.015523714275459968</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0.00031955417889801413</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10">
-        <v>-1.0166065633437447</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0.002059840927860151</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11">
-        <v>-0.047132240753353011</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0.00073282214930691649</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>72</v>
-      </c>
       <c r="B12">
-        <v>-0.27669602583764091</v>
+        <v>-0.21260703912357981</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -2700,254 +1678,29 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.014215875610528226</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13">
-        <v>-0.27952443248187853</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0.11765704616836628</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14">
-        <v>0.087346586311286251</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0.046303877879908466</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15">
-        <v>0.34174557800829464</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0.044504718118173033</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16">
-        <v>0.12154708196163619</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0.02061715809331233</v>
+        <v>0.0056332944711536531</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B37"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1">
+      <c r="A1" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+    <row r="3">
+      <c r="A3" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>60</v>
       </c>
@@ -2955,7 +1708,7 @@
         <v>0.38973643300107141</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -2963,20 +1716,20 @@
         <v>217589</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+    <row r="7">
+      <c r="A7" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>60</v>
       </c>
       <c r="B8">
-        <v>0.62630994913170568</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+        <v>0.62593290185532879</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -2984,20 +1737,20 @@
         <v>98541</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+    <row r="11">
+      <c r="A11" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>60</v>
       </c>
       <c r="B12">
-        <v>0.6375643558530979</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+        <v>0.63711064205966306</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -3005,12 +1758,12 @@
         <v>83407</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
+    <row r="15">
+      <c r="A15" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>60</v>
       </c>
@@ -3018,7 +1771,7 @@
         <v>0.5422928670837408</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>61</v>
       </c>
@@ -3026,20 +1779,20 @@
         <v>217589</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
+    <row r="19">
+      <c r="A19" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>60</v>
       </c>
       <c r="B20">
-        <v>0.7392147515141112</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.25">
+        <v>0.73900352102504496</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
         <v>61</v>
       </c>
@@ -3047,20 +1800,20 @@
         <v>98541</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.25">
+    <row r="23">
+      <c r="A23" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s">
         <v>60</v>
       </c>
       <c r="B24">
-        <v>0.71655057041170878</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.25">
+        <v>0.71627271000620119</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -3068,12 +1821,12 @@
         <v>83407</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.25">
-      <c r="A27" s="24" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.25">
+    <row r="27">
+      <c r="A27" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -3081,7 +1834,7 @@
         <v>0.26549924576278161</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -3089,20 +1842,20 @@
         <v>217589</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.25">
-      <c r="A31" s="25" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.25">
+    <row r="31">
+      <c r="A31" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" t="s">
         <v>60</v>
       </c>
       <c r="B32">
-        <v>0.53857747493423158</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.25">
+        <v>0.53829952694824534</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -3110,20 +1863,20 @@
         <v>98541</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="35" x14ac:dyDescent="0.25">
-      <c r="A35" s="26" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="36" x14ac:dyDescent="0.25">
+    <row r="35">
+      <c r="A35" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" t="s">
         <v>60</v>
       </c>
       <c r="B36">
-        <v>0.53816928204339321</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="37" x14ac:dyDescent="0.25">
+        <v>0.53798497462488526</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" t="s">
         <v>61</v>
       </c>
@@ -3132,16 +1885,15 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AH33"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -3245,7 +1997,7 @@
         <v>58</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -3349,7 +2101,7 @@
         <v>-0.025970706367143194</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -3453,7 +2205,7 @@
         <v>0.00036226261076840045</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -3557,7 +2309,7 @@
         <v>-0.0052316647195785604</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -3661,7 +2413,7 @@
         <v>5.8072470927370961e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -3765,7 +2517,7 @@
         <v>-0.00075219862648130448</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -3869,7 +2621,7 @@
         <v>-0.00069534657074768686</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -3973,7 +2725,7 @@
         <v>-0.0033110064832434149</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -4077,7 +2829,7 @@
         <v>-0.0065274792857330111</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -4181,7 +2933,7 @@
         <v>0.00084072845059991275</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -4285,7 +3037,7 @@
         <v>-0.0086122058169163709</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -4389,7 +3141,7 @@
         <v>0.0025049456405566747</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -4493,7 +3245,7 @@
         <v>-0.0087175070027589591</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -4597,7 +3349,7 @@
         <v>-0.0047257353288733062</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -4701,7 +3453,7 @@
         <v>-0.0018128370326831421</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -4805,7 +3557,7 @@
         <v>-0.00070853779059918266</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -4909,7 +3661,7 @@
         <v>-0.011198921217637913</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -5013,7 +3765,7 @@
         <v>-0.012520851135024866</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -5117,7 +3869,7 @@
         <v>-0.012046011281103847</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -5221,7 +3973,7 @@
         <v>-0.01204883225879802</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -5325,7 +4077,7 @@
         <v>-0.010294612318902042</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -5429,7 +4181,7 @@
         <v>-0.010898907850681136</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -5533,7 +4285,7 @@
         <v>-0.011157373034846409</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -5637,7 +4389,7 @@
         <v>-0.01177219685282186</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -5741,7 +4493,7 @@
         <v>-0.010462455812284025</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -5845,7 +4597,7 @@
         <v>-0.012951990907545924</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -5949,7 +4701,7 @@
         <v>-0.012106396041294184</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -6053,7 +4805,7 @@
         <v>-0.010713748217050293</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -6157,7 +4909,7 @@
         <v>-0.00087693070388110796</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>55</v>
       </c>
@@ -6261,7 +5013,7 @@
         <v>-0.0070248979435880033</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>56</v>
       </c>
@@ -6365,7 +5117,7 @@
         <v>-0.0049155078152701686</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>57</v>
       </c>
@@ -6469,7 +5221,7 @@
         <v>-0.012394941842145103</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>58</v>
       </c>
@@ -6574,16 +5326,15 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -6591,587 +5342,455 @@
         <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>63</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2">
+        <v>0.47566669465274541</v>
+      </c>
+      <c r="C2">
+        <v>0.035615908761922339</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>64</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B3">
+        <v>1.6060005684327254</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0.063817736714186127</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>65</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B4">
+        <v>0.32301114311557377</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0.04074819810866348</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>66</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B5">
+        <v>0.017778718274035842</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0.025474028395478157</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>67</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B6">
+        <v>0.11025513173645315</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0.042624174932086235</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
         <v>68</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B7">
+        <v>0.2046518247469398</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0.0481861247354839</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
         <v>69</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B8">
+        <v>-0.13128885389975622</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.0051925827744242689</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
         <v>70</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B9">
+        <v>-0.10027872559874583</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.00577016664299684</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
         <v>71</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B10">
+        <v>-3.1582228421508622</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.025943904463164268</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
         <v>72</v>
       </c>
-      <c r="N1" t="s">
+      <c r="B11">
+        <v>-0.15296768731928445</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.011881720143412171</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
         <v>73</v>
       </c>
-      <c r="O1" t="s">
-        <v>74</v>
-      </c>
-      <c r="P1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2">
-        <v>-0.066582047710028181</v>
-      </c>
-      <c r="C2">
-        <v>0.1175866126774384</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3">
-        <v>1.000147364670801</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0.13485851793284259</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4">
-        <v>0.42399270501976533</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0.040996588008941362</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5">
-        <v>0.028692386465289235</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0.025413225140113283</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6">
-        <v>0.11379411657150687</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0.042493203615728031</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7">
-        <v>0.2184474789361173</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0.04782310336377392</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8">
-        <v>-0.13554395722904289</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0.0051954116483734596</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9">
-        <v>-0.087407482804515532</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0.0058017255185404473</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10">
-        <v>-3.1579021391312092</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0.025723810069399798</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11">
-        <v>-0.19400172734012222</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0.011847367618376691</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>72</v>
-      </c>
       <c r="B12">
-        <v>-1.9448983473064443</v>
+        <v>-1.2604802142992511</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -7204,244 +5823,19 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.15594079927988852</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13">
-        <v>1.5020273130492214</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>1.0823117594381626</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14">
-        <v>1.582904872707493</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0.44209388715871006</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15">
-        <v>0.14861378823629379</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0.60986427634310603</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16">
-        <v>1.6391099011269059</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0.51957667982726985</v>
+        <v>0.082194595910492038</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -7449,587 +5843,455 @@
         <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>63</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2">
+        <v>0.58862098200147817</v>
+      </c>
+      <c r="C2">
+        <v>0.056115550629910055</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>64</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B3">
+        <v>1.3839880444918631</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0.11434513310804352</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>65</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B4">
+        <v>0.2284016893588294</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0.087681575182568</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>66</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B5">
+        <v>-0.041619127661210301</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0.032773433143403918</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>67</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B6">
+        <v>-0.036218053655162265</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0.049597161335729348</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
         <v>68</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B7">
+        <v>0.062237170141363679</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0.063428127952435992</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
         <v>69</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B8">
+        <v>-0.03736412375756528</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.0050384133701462317</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
         <v>70</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B9">
+        <v>-0.012860565931171512</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.0048444637027786073</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
         <v>71</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B10">
+        <v>-3.1770315436553265</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.035832689280218308</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
         <v>72</v>
       </c>
-      <c r="N1" t="s">
+      <c r="B11">
+        <v>-0.29141658400614218</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.013803158029160911</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
         <v>73</v>
       </c>
-      <c r="O1" t="s">
-        <v>74</v>
-      </c>
-      <c r="P1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2">
-        <v>-0.61113010310016602</v>
-      </c>
-      <c r="C2">
-        <v>0.30268295129156259</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3">
-        <v>0.13132582507924812</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0.34877810247438379</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4">
-        <v>0.32568967017275469</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0.085005831544376936</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5">
-        <v>-0.057572968035823152</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0.032826764356510184</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6">
-        <v>-0.049808309939651983</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0.049463138745464263</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7">
-        <v>0.070026336133024392</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0.063711562347698522</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8">
-        <v>-0.034376712083511882</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0.0050323110002492635</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9">
-        <v>-0.016006590256730974</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0.0048382814170224607</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10">
-        <v>-3.1468593794064277</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0.03545744817426446</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11">
-        <v>-0.30207706017377256</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0.013848689437913795</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>72</v>
-      </c>
       <c r="B12">
-        <v>-3.4435754393922933</v>
+        <v>-2.0790594151796999</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -8062,244 +6324,19 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.47573447863497398</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13">
-        <v>1.8664544237354446</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>2.3868441766165351</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14">
-        <v>3.9683150475538276</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>1.3525809473887243</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15">
-        <v>3.9755771436885254</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>1.3037037695780493</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16">
-        <v>1.9804425828440278</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0.71760663544553471</v>
+        <v>0.1449976591419585</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AH33"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -8403,7 +6440,7 @@
         <v>58</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -8507,7 +6544,7 @@
         <v>-0.012499400476602078</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -8611,7 +6648,7 @@
         <v>-2.6462480285482546e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -8715,7 +6752,7 @@
         <v>-0.0029397083838439749</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -8819,7 +6856,7 @@
         <v>3.2639603295941345e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -8923,7 +6960,7 @@
         <v>-0.00038395605402854311</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -9027,7 +7064,7 @@
         <v>-0.00087904039794668481</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -9131,7 +7168,7 @@
         <v>-0.0039668697025457226</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -9235,7 +7272,7 @@
         <v>-0.0065738141814511031</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -9339,7 +7376,7 @@
         <v>0.00037936048187465739</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -9443,7 +7480,7 @@
         <v>-0.0068906677880312649</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -9547,7 +7584,7 @@
         <v>0.00086077840601086314</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -9651,7 +7688,7 @@
         <v>-0.0047612065671378007</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -9755,7 +7792,7 @@
         <v>-0.0021920924041388297</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -9859,7 +7896,7 @@
         <v>-0.0005095374714178156</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -9963,7 +8000,7 @@
         <v>3.1640151975952807e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -10067,7 +8104,7 @@
         <v>-0.012095624238222247</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -10171,7 +8208,7 @@
         <v>-0.0055288106463826405</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -10275,7 +8312,7 @@
         <v>-0.0066914966525110121</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -10379,7 +8416,7 @@
         <v>-0.0065697590319152141</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -10483,7 +8520,7 @@
         <v>-0.0055253095162253272</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -10587,7 +8624,7 @@
         <v>-0.0062591865676181859</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -10691,7 +8728,7 @@
         <v>-0.0070592379424617669</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -10795,7 +8832,7 @@
         <v>-0.0064247175428402423</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -10899,7 +8936,7 @@
         <v>-0.0061334186231454596</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -11003,7 +9040,7 @@
         <v>-0.00811015283437206</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -11107,7 +9144,7 @@
         <v>-0.0058161975372637001</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -11211,7 +9248,7 @@
         <v>-0.00587945832773703</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -11315,7 +9352,7 @@
         <v>-0.00056921490202321531</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>55</v>
       </c>
@@ -11419,7 +9456,7 @@
         <v>-0.0056941139442822945</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>56</v>
       </c>
@@ -11523,7 +9560,7 @@
         <v>-0.0026951697411917879</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>57</v>
       </c>
@@ -11627,7 +9664,7 @@
         <v>-0.0063882918775172194</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>58</v>
       </c>
@@ -11732,16 +9769,15 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -11749,587 +9785,455 @@
         <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>63</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2">
+        <v>0.89840235129929091</v>
+      </c>
+      <c r="C2">
+        <v>0.025902540255599516</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>64</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B3">
+        <v>1.0780300757050752</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0.048460446671764849</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>65</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B4">
+        <v>-0.025775837779279356</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0.03565408689377602</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>66</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B5">
+        <v>0.096247479993237045</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0.020210299026599141</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>67</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B6">
+        <v>-0.0036567547763086926</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0.033052891121425766</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
         <v>68</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B7">
+        <v>0.030279665336521291</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0.042462631311151709</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
         <v>69</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B8">
+        <v>0.05148530414459418</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.0036071643081563368</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
         <v>70</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B9">
+        <v>0.001877667387111462</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.004316020936498661</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
         <v>71</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B10">
+        <v>-0.010011999171150086</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.020396252086797625</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
         <v>72</v>
       </c>
-      <c r="N1" t="s">
+      <c r="B11">
+        <v>-0.25199440458991301</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.0083434926553822651</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
         <v>73</v>
       </c>
-      <c r="O1" t="s">
-        <v>74</v>
-      </c>
-      <c r="P1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2">
-        <v>0.41148590958104647</v>
-      </c>
-      <c r="C2">
-        <v>0.078582202068161522</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3">
-        <v>0.61056527238297131</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0.096629532100188639</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4">
-        <v>0.00293160470964392</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0.035880973744350918</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5">
-        <v>0.085862541397877357</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0.020221345854662655</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6">
-        <v>-0.013384115900563848</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0.033010990813895788</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7">
-        <v>0.046008275708261701</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0.042113356265020052</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8">
-        <v>0.057525128583661517</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0.0036032521987172245</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9">
-        <v>-0.01122122944840297</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0.0043287132318025317</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10">
-        <v>0.014633138948031373</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0.02027644892408419</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11">
-        <v>-0.25203700389718198</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0.0082985077849093703</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>72</v>
-      </c>
       <c r="B12">
-        <v>-2.9038359933834483</v>
+        <v>-2.0411922956409119</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -12362,244 +10266,19 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.14970523113053572</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13">
-        <v>0.78352973719452579</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>1.0018419748560665</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14">
-        <v>1.8030234560249163</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0.42179678837971618</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15">
-        <v>1.9278939317261135</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0.51261471615705834</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16">
-        <v>1.8787609869787743</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0.4523292042963169</v>
+        <v>0.073847445062495035</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -12607,587 +10286,455 @@
         <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>63</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2">
+        <v>0.5405026665677477</v>
+      </c>
+      <c r="C2">
+        <v>0.037877912956836991</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>64</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B3">
+        <v>0.6357320430908322</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0.080765312995277824</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>65</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B4">
+        <v>-0.2413167727605052</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0.052702642423927186</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>66</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B5">
+        <v>-0.063944805120900672</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0.02641424455765402</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>67</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B6">
+        <v>0.12119672476177736</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0.043575155912568241</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
         <v>68</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B7">
+        <v>-0.2701278900889369</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0.054112535157103687</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
         <v>69</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B8">
+        <v>0.05088388872484844</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.0036132211862245447</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
         <v>70</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B9">
+        <v>-0.03079207162722826</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.0053018923044098817</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
         <v>71</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B10">
+        <v>-0.33092174197850077</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.026264115862572702</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
         <v>72</v>
       </c>
-      <c r="N1" t="s">
+      <c r="B11">
+        <v>-0.36343768177414904</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.0079284455869108091</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
         <v>73</v>
       </c>
-      <c r="O1" t="s">
-        <v>74</v>
-      </c>
-      <c r="P1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2">
-        <v>0.244675790989863</v>
-      </c>
-      <c r="C2">
-        <v>0.12629447674049921</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3">
-        <v>0.30605594127223046</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0.16480037472270792</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4">
-        <v>-0.21117979719930705</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0.053064612846111095</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5">
-        <v>-0.080248908639936917</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0.026328746258117399</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6">
-        <v>0.10394064924005336</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0.043369309230387496</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7">
-        <v>-0.2654988251213361</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0.053645214021550723</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8">
-        <v>0.05289707270263324</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0.0036055574493486999</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9">
-        <v>-0.033086236067255685</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0.0053553210654226071</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10">
-        <v>-0.30343011673411463</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0.026253492512482685</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11">
-        <v>-0.37195270352951759</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0.0078985745190204779</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>72</v>
-      </c>
       <c r="B12">
-        <v>-2.8562631839580424</v>
+        <v>-1.6421423450994828</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -13220,244 +10767,19 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.40576513928228547</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13">
-        <v>1.3561888967220617</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>1.6179530273302349</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14">
-        <v>1.0379303727131683</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>1.1215428057809957</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15">
-        <v>2.0921562828071525</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>1.2863718658543459</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16">
-        <v>2.4137699592735582</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0.57619189106339819</v>
+        <v>0.11151769679780131</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AH33"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -13477,7 +10799,7 @@
         <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H1" t="s">
         <v>32</v>
@@ -13561,7 +10883,7 @@
         <v>58</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -13665,7 +10987,7 @@
         <v>-0.0010670823432967916</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -13769,7 +11091,7 @@
         <v>-6.0056187532480907e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -13873,7 +11195,7 @@
         <v>-0.0002444851921972353</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -13977,9 +11299,9 @@
         <v>2.7061832319159491e-06</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B6">
         <v>0.40644088966074837</v>
@@ -14081,7 +11403,7 @@
         <v>-0.00010773418717360402</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -14185,7 +11507,7 @@
         <v>-2.9017589037477306e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -14289,7 +11611,7 @@
         <v>-0.0002035887947088337</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -14393,7 +11715,7 @@
         <v>-0.00029004144576150106</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -14497,7 +11819,7 @@
         <v>-5.5852288505335961e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -14601,7 +11923,7 @@
         <v>-0.00042529789984287024</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -14705,7 +12027,7 @@
         <v>9.4648935657562041e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -14809,7 +12131,7 @@
         <v>-0.00032247074729740028</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -14913,7 +12235,7 @@
         <v>-0.00017367867826829057</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -15017,7 +12339,7 @@
         <v>-9.4707033103206956e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -15121,7 +12443,7 @@
         <v>-2.3977199923479469e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -15225,7 +12547,7 @@
         <v>-0.0003795453882827237</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -15329,7 +12651,7 @@
         <v>-0.00055685064559722998</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -15433,7 +12755,7 @@
         <v>-0.00053549027508007136</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -15537,7 +12859,7 @@
         <v>-0.00053256563339348863</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -15641,7 +12963,7 @@
         <v>-0.00048669478605278436</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -15745,7 +13067,7 @@
         <v>-0.00050665474184486369</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -15849,7 +13171,7 @@
         <v>-0.00055784020266723107</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -15953,7 +13275,7 @@
         <v>-0.00050971479709542534</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -16057,7 +13379,7 @@
         <v>-0.00049630531949580595</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -16161,7 +13483,7 @@
         <v>-0.00059735324959790757</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -16265,7 +13587,7 @@
         <v>-0.00049601865691121909</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -16369,7 +13691,7 @@
         <v>-0.00052752092976152598</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -16473,7 +13795,7 @@
         <v>-2.4895533987548276e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>55</v>
       </c>
@@ -16577,7 +13899,7 @@
         <v>-0.00027644464410517326</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>56</v>
       </c>
@@ -16681,7 +14003,7 @@
         <v>-0.00037984779983171052</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>57</v>
       </c>
@@ -16785,7 +14107,7 @@
         <v>-0.00029986101865586966</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>58</v>
       </c>
@@ -16890,6 +14212,5 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>